--- a/sheets/대금율보/검수/안동역에서.xlsx
+++ b/sheets/대금율보/검수/안동역에서.xlsx
@@ -4641,7 +4641,7 @@
       <c r="A4" s="0"/>
       <c r="B4" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–汰‹
+          <t xml:space="preserve">–汰
 淋</t>
         </is>
       </c>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="F4" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–浹‹
+          <t xml:space="preserve">–浹
 汰</t>
         </is>
       </c>
@@ -4695,7 +4695,7 @@
       <c r="A5" s="0"/>
       <c r="B5" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–湳‹
+          <t xml:space="preserve">–湳
 潢</t>
         </is>
       </c>
@@ -4717,7 +4717,7 @@
       <c r="F5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–浹
-–汰‹</t>
+–汰</t>
         </is>
       </c>
       <c r="G5" s="25" t="inlineStr">
@@ -4915,7 +4915,7 @@
       <c r="I10" s="26"/>
       <c r="J10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 無南</t>
         </is>
       </c>
@@ -4970,7 +4970,7 @@
       <c r="J11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">林南
-林‹</t>
+林</t>
         </is>
       </c>
       <c r="K11" s="24"/>
@@ -5095,8 +5095,8 @@
       </c>
       <c r="D14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–潢‹
-–潕‹</t>
+          <t xml:space="preserve">–潢
+–潕</t>
         </is>
       </c>
       <c r="E14" s="26" t="inlineStr">
@@ -5108,7 +5108,7 @@
       <c r="G14" s="26"/>
       <c r="H14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–㳞‹
+          <t xml:space="preserve">–㳞
 –浹</t>
         </is>
       </c>
@@ -5179,7 +5179,7 @@
       <c r="E16" s="25"/>
       <c r="F16" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕‹
+          <t xml:space="preserve">潕
 –湳</t>
         </is>
       </c>
@@ -5224,11 +5224,7 @@
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="H17" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H17" s="23"/>
       <c r="I17" s="25"/>
       <c r="J17" s="23" t="inlineStr">
         <is>
@@ -5325,7 +5321,7 @@
       <c r="C20" s="25"/>
       <c r="D20" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–潕‹
+          <t xml:space="preserve">–潕
 湳</t>
         </is>
       </c>
@@ -5348,7 +5344,7 @@
       <c r="H20" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-淋‹</t>
+淋</t>
         </is>
       </c>
       <c r="I20" s="25" t="inlineStr">
@@ -5368,13 +5364,13 @@
       <c r="A21" s="0"/>
       <c r="B21" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳‹</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="C21" s="25"/>
       <c r="D21" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–淋‹
+          <t xml:space="preserve">–淋
 淋</t>
         </is>
       </c>
@@ -5386,7 +5382,7 @@
       <c r="F21" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">浹淋
-–‹</t>
+–</t>
         </is>
       </c>
       <c r="G21" s="25" t="inlineStr">
@@ -5416,7 +5412,7 @@
       <c r="A22" s="0"/>
       <c r="B22" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕‹</t>
+          <t xml:space="preserve">潕</t>
         </is>
       </c>
       <c r="C22" s="26"/>
@@ -5433,7 +5429,7 @@
       </c>
       <c r="F22" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–㳞‹
+          <t xml:space="preserve">–㳞
 –浹</t>
         </is>
       </c>
@@ -5519,7 +5515,7 @@
       <c r="C24" s="25"/>
       <c r="D24" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–淋‹
+          <t xml:space="preserve">–淋
 –浹</t>
         </is>
       </c>
@@ -5528,11 +5524,7 @@
           <t xml:space="preserve">녹는</t>
         </is>
       </c>
-      <c r="F24" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F24" s="23"/>
       <c r="G24" s="25"/>
       <c r="H24" s="23" t="inlineStr">
         <is>

--- a/sheets/대금율보/검수/안동역에서.xlsx
+++ b/sheets/대금율보/검수/안동역에서.xlsx
@@ -4551,22 +4551,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="15.29" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="15.29" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="15.29" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="15.29" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="15.29" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="93.02" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
       <c r="J2" s="20"/>
       <c r="K2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="69.36" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
       </c>
       <c r="K3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="69.36" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="23" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="K4" s="25"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="69.36" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="23" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="K5" s="25"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="69.36" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="23" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
       <c r="J6" s="23"/>
       <c r="K6" s="26"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="69.36" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="23"/>
       <c r="C7" s="24"/>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="K7" s="24"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="69.36" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="23"/>
       <c r="C8" s="25"/>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="K8" s="25"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="69.36" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="23" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
       </c>
       <c r="K9" s="25"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="69.36" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="K10" s="26"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="69.36" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="23" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="K11" s="24"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="69.36" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="23" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
       </c>
       <c r="K12" s="28"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="69.36" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="23" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
       </c>
       <c r="K13" s="25"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="69.36" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="23" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
       <c r="J14" s="23"/>
       <c r="K14" s="26"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="69.36" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="23" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="K15" s="24"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="69.36" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="23"/>
       <c r="C16" s="25"/>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="K16" s="25"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="69.36" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="23" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="K17" s="25"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="69.36" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="23" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
       <c r="J18" s="23"/>
       <c r="K18" s="26"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="69.36" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="23" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="K19" s="24"/>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="69.36" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="23" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
       </c>
       <c r="K20" s="25"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="69.36" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="23" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
       </c>
       <c r="K21" s="25"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="69.36" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="23" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="K22" s="26"/>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="69.36" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="K23" s="24"/>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="69.36" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="23" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
       <c r="J24" s="23"/>
       <c r="K24" s="25"/>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="69.36" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="23" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="K25" s="25"/>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="69.36" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21" t="inlineStr">
         <is>
@@ -5614,6 +5614,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="52"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="43"/>
 </worksheet>
 </file>